--- a/financials/PNJ/PNJ_Q.xlsx
+++ b/financials/PNJ/PNJ_Q.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="12000" yWindow="4785" windowWidth="12000" windowHeight="8115" tabRatio="600" firstSheet="4" activeTab="5" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="4545" windowWidth="24000" windowHeight="8355" tabRatio="600" firstSheet="3" activeTab="4" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="balance_sheet" sheetId="1" state="visible" r:id="rId1"/>
@@ -13,10 +13,6 @@
     <sheet name="Dự phóng tăng trưởng" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Sheet1" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId7"/>
-    <externalReference r:id="rId8"/>
-  </externalReferences>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -358,7 +354,7 @@
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Percent" xfId="2" builtinId="5"/>
   </cellStyles>
-  <dxfs count="22">
+  <dxfs count="18">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -489,38 +485,6 @@
         </patternFill>
       </fill>
     </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="9"/>
-          <bgColor theme="9"/>
-        </patternFill>
-      </fill>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -592,59 +556,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook r:id="rId1">
-    <sheetNames>
-      <sheetName val="Sheet1"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="2">
-          <cell r="B2">
-            <v>21850</v>
-          </cell>
-          <cell r="E2">
-            <v>32650</v>
-          </cell>
-        </row>
-      </sheetData>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <externalBook r:id="rId1">
-    <sheetNames>
-      <sheetName val="CĐKT"/>
-      <sheetName val="KQHĐKD"/>
-      <sheetName val="LCTT"/>
-      <sheetName val="Tổng quan"/>
-      <sheetName val="Dự báo tăng trưởng"/>
-      <sheetName val="Hiệu quả thực hiện KH"/>
-      <sheetName val="Số CH"/>
-      <sheetName val="Chart"/>
-      <sheetName val="Phân tích"/>
-      <sheetName val="Chỉ số"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3"/>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -14677,41 +14588,32 @@
           <t>Thị giá</t>
         </is>
       </c>
-      <c r="B3" s="27">
-        <f>[1]Sheet1!$E$2</f>
-        <v/>
-      </c>
-      <c r="C3" s="27">
-        <f>[1]Sheet1!$E$2</f>
-        <v/>
-      </c>
-      <c r="D3" s="27">
-        <f>[1]Sheet1!$E$2</f>
-        <v/>
-      </c>
-      <c r="E3" s="27">
-        <f>[1]Sheet1!$E$2</f>
-        <v/>
-      </c>
-      <c r="F3" s="27">
-        <f>[1]Sheet1!$E$2</f>
-        <v/>
-      </c>
-      <c r="G3" s="27">
-        <f>[1]Sheet1!$E$2</f>
-        <v/>
-      </c>
-      <c r="H3" s="27">
-        <f>[1]Sheet1!$E$2</f>
-        <v/>
-      </c>
-      <c r="I3" s="27">
-        <f>[1]Sheet1!$E$2</f>
-        <v/>
-      </c>
-      <c r="J3" s="27">
-        <f>[1]Sheet1!$E$2</f>
-        <v/>
+      <c r="B3" s="27" t="n">
+        <v>32650</v>
+      </c>
+      <c r="C3" s="27" t="n">
+        <v>32650</v>
+      </c>
+      <c r="D3" s="27" t="n">
+        <v>32650</v>
+      </c>
+      <c r="E3" s="27" t="n">
+        <v>32650</v>
+      </c>
+      <c r="F3" s="27" t="n">
+        <v>32650</v>
+      </c>
+      <c r="G3" s="27" t="n">
+        <v>32650</v>
+      </c>
+      <c r="H3" s="27" t="n">
+        <v>32650</v>
+      </c>
+      <c r="I3" s="27" t="n">
+        <v>32650</v>
+      </c>
+      <c r="J3" s="27" t="n">
+        <v>32650</v>
       </c>
     </row>
     <row r="4">
@@ -14808,7 +14710,10 @@
           <t>LICĐKKS</t>
         </is>
       </c>
-      <c r="B7" s="25" t="n"/>
+      <c r="B7" s="25">
+        <f>chi_so_tai_chinh!I41</f>
+        <v/>
+      </c>
       <c r="C7" s="62" t="n">
         <v>0</v>
       </c>
@@ -14830,9 +14735,8 @@
       <c r="I7" s="62" t="n">
         <v>0</v>
       </c>
-      <c r="J7" s="62">
-        <f>[2]CĐKT!J135*1000000000</f>
-        <v/>
+      <c r="J7" s="62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
